--- a/dados_requisitos_lista.xlsx
+++ b/dados_requisitos_lista.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="E1" sheetId="1" state="visible" r:id="rId3"/>
@@ -105,7 +105,6 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">DESCRIÇÃO DOS CRITEIROS
 </t>
@@ -292,7 +291,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,12 +326,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -855,7 +848,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>12</v>
@@ -927,7 +920,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>15</v>
@@ -1385,15 +1378,15 @@
       <formula1>DADOS!$D$2:$D$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F33" type="list">
-      <formula1>DADOS!$M$2:$M$8</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G33" type="list">
       <formula1>DADOS!$P$2:$P$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E33" type="list">
+      <formula1>DADOS!$M$2:$M$8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F33" type="list">
       <formula1>DADOS!$M$2:$M$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1508,7 +1501,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
@@ -1628,7 +1621,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>11</v>
@@ -1700,7 +1693,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>11</v>
@@ -1724,7 +1717,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>11</v>
@@ -1820,7 +1813,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>11</v>
@@ -1844,7 +1837,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>11</v>
@@ -1964,7 +1957,7 @@
         <v>35</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>11</v>
@@ -1988,7 +1981,7 @@
         <v>36</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>15</v>
@@ -2223,19 +2216,19 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C33" type="list">
-      <formula1>#ref!</formula1>
+      <formula1>DADOS!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D33" type="list">
-      <formula1>#ref!</formula1>
+      <formula1>DADOS!$D$2:$D$8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G33" type="list">
+      <formula1>DADOS!$P$2:$P$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:F33" type="list">
-      <formula1>#ref!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G33" type="list">
-      <formula1>#ref!</formula1>
+      <formula1>DADOS!$M$2:$M$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3107,7 +3100,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="83.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
